--- a/data/trans_dic/P13_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,95</t>
+          <t>4,15; 7,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,24</t>
+          <t>5,73; 9,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,81</t>
+          <t>4,44; 7,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,31</t>
+          <t>9,97; 14,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,65</t>
+          <t>5,92; 8,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 16,98</t>
+          <t>13,17; 17,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,76</t>
+          <t>8,73; 12,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 20,14</t>
+          <t>15,84; 19,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,44</t>
+          <t>5,38; 7,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,12</t>
+          <t>10,45; 13,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,01</t>
+          <t>7,28; 10,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 17,17</t>
+          <t>13,91; 17,14</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,05</t>
+          <t>1,63; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,92</t>
+          <t>3,02; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,72</t>
+          <t>2,07; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,36</t>
+          <t>2,35; 4,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,13</t>
+          <t>2,43; 4,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,69</t>
+          <t>5,14; 7,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,55</t>
+          <t>2,72; 4,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,21</t>
+          <t>3,21; 5,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,39</t>
+          <t>2,22; 3,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,84</t>
+          <t>4,35; 5,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,79</t>
+          <t>2,65; 3,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,61</t>
+          <t>3,13; 4,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,45</t>
+          <t>0,88; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,72</t>
+          <t>1,47; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,08</t>
+          <t>1,25; 4,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,84</t>
+          <t>2,57; 5,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,01</t>
+          <t>2,35; 5,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,7</t>
+          <t>1,88; 5,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,32</t>
+          <t>1,99; 5,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,07</t>
+          <t>1,97; 4,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,97</t>
+          <t>1,96; 4,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,6</t>
+          <t>2,07; 4,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,22</t>
+          <t>2,05; 4,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,37</t>
+          <t>2,59; 4,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,83</t>
+          <t>2,63; 3,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,43</t>
+          <t>3,95; 5,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,2</t>
+          <t>2,9; 4,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,74</t>
+          <t>3,77; 5,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,61</t>
+          <t>4,17; 5,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 10,17</t>
+          <t>8,25; 10,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,44</t>
+          <t>4,81; 6,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 7,65</t>
+          <t>5,65; 7,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,56</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,65</t>
+          <t>6,41; 7,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,04</t>
+          <t>4,06; 5,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,55</t>
+          <t>5,01; 6,51</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42042; 71744</t>
+          <t>42861; 72374</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53853; 89993</t>
+          <t>55751; 90527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34236; 58945</t>
+          <t>33496; 59597</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50148; 78729</t>
+          <t>51258; 76725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78234; 113748</t>
+          <t>77802; 115345</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>173958; 226968</t>
+          <t>176058; 228953</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86697; 126627</t>
+          <t>86696; 127271</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>120470; 151546</t>
+          <t>119161; 149221</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126000; 174522</t>
+          <t>126337; 174716</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>239379; 303052</t>
+          <t>241447; 304594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127762; 174872</t>
+          <t>127173; 175286</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>177115; 217480</t>
+          <t>176126; 217076</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27164; 51595</t>
+          <t>27629; 53954</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59073; 96434</t>
+          <t>59194; 94701</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44595; 77110</t>
+          <t>42971; 76213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54291; 99761</t>
+          <t>53861; 98649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37244; 65579</t>
+          <t>38652; 67648</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91609; 135090</t>
+          <t>90226; 132975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55494; 90434</t>
+          <t>54041; 88501</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69505; 116605</t>
+          <t>71751; 119766</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73155; 111134</t>
+          <t>72995; 110867</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159747; 217204</t>
+          <t>161703; 217308</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107980; 153848</t>
+          <t>107506; 153648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>139443; 208767</t>
+          <t>141726; 207755</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4677; 19022</t>
+          <t>4850; 19295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7591; 22724</t>
+          <t>7068; 23564</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6529; 22304</t>
+          <t>6837; 22832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16599; 37757</t>
+          <t>16604; 36649</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11089; 28654</t>
+          <t>11192; 28321</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9115; 26120</t>
+          <t>8623; 26376</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10358; 29123</t>
+          <t>10877; 30234</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13941; 26900</t>
+          <t>13042; 27184</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19945; 40838</t>
+          <t>20102; 41297</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19633; 43214</t>
+          <t>19412; 43157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21112; 46189</t>
+          <t>22467; 48097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33737; 57178</t>
+          <t>33822; 58296</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85961; 125506</t>
+          <t>86111; 127563</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>134151; 185426</t>
+          <t>134848; 187010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95224; 141781</t>
+          <t>98048; 140993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>127411; 197834</t>
+          <t>129970; 196238</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>137011; 189635</t>
+          <t>140887; 192328</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>294577; 361267</t>
+          <t>292961; 363203</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>168395; 227271</t>
+          <t>169542; 223629</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>204923; 278993</t>
+          <t>206116; 279033</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>238296; 303755</t>
+          <t>237495; 301003</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>443556; 533177</t>
+          <t>446865; 534063</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>276423; 348098</t>
+          <t>280127; 349906</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>361056; 464596</t>
+          <t>355611; 462026</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,01</t>
+          <t>3,97; 7,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,3</t>
+          <t>5,6; 9,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,9</t>
+          <t>4,46; 7,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 14,93</t>
+          <t>9,26; 14,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,77</t>
+          <t>5,74; 8,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,17; 17,13</t>
+          <t>13,29; 17,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,82</t>
+          <t>8,64; 12,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 19,83</t>
+          <t>15,96; 19,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,44</t>
+          <t>5,33; 7,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 13,18</t>
+          <t>10,32; 13,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,03</t>
+          <t>7,4; 9,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,91; 17,14</t>
+          <t>13,73; 16,84</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,19</t>
+          <t>1,63; 3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,83</t>
+          <t>2,98; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,67</t>
+          <t>2,08; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,31</t>
+          <t>3,22; 5,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,26</t>
+          <t>2,44; 4,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,57</t>
+          <t>5,08; 7,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,45</t>
+          <t>2,72; 4,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,36</t>
+          <t>4,21; 5,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,38</t>
+          <t>2,21; 3,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 5,85</t>
+          <t>4,36; 5,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,78</t>
+          <t>2,61; 3,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,59</t>
+          <t>3,96; 5,14</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,5</t>
+          <t>0,99; 3,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,9</t>
+          <t>1,49; 4,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,17</t>
+          <t>1,08; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,67</t>
+          <t>2,63; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,94</t>
+          <t>2,36; 5,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,75</t>
+          <t>1,93; 5,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,52</t>
+          <t>2,09; 5,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,12</t>
+          <t>2,24; 4,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,02</t>
+          <t>1,93; 3,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,59</t>
+          <t>1,96; 4,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,4</t>
+          <t>2,06; 4,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,46</t>
+          <t>2,69; 4,38</t>
         </is>
       </c>
     </row>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,85%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,25%</t>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,89</t>
+          <t>2,59; 3,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,47</t>
+          <t>3,95; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,18</t>
+          <t>2,87; 4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,69</t>
+          <t>4,53; 6,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,69</t>
+          <t>4,15; 5,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,23</t>
+          <t>8,29; 10,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,34</t>
+          <t>4,74; 6,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,65</t>
+          <t>6,78; 8,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,52</t>
+          <t>3,54; 4,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,66</t>
+          <t>6,33; 7,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,07</t>
+          <t>4,03; 5,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,51</t>
+          <t>5,87; 6,88</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62816</t>
+          <t>66029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>146060</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>196280</t>
+          <t>212089</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42861; 72374</t>
+          <t>40996; 72241</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55751; 90527</t>
+          <t>54500; 88999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33496; 59597</t>
+          <t>33628; 58169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51258; 76725</t>
+          <t>53468; 80920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77802; 115345</t>
+          <t>75498; 114057</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>176058; 228953</t>
+          <t>177674; 228109</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86696; 127271</t>
+          <t>85729; 125820</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>119161; 149221</t>
+          <t>130652; 162477</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126337; 174716</t>
+          <t>125053; 175295</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>241447; 304594</t>
+          <t>238509; 302483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127173; 175286</t>
+          <t>129231; 174591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>176126; 217076</t>
+          <t>191650; 235127</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79677</t>
+          <t>90660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96191</t>
+          <t>107998</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>175868</t>
+          <t>198658</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27629; 53954</t>
+          <t>27676; 54368</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59194; 94701</t>
+          <t>58429; 92248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42971; 76213</t>
+          <t>43227; 77693</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53861; 98649</t>
+          <t>71678; 113166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38652; 67648</t>
+          <t>38666; 67385</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90226; 132975</t>
+          <t>89127; 132383</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54041; 88501</t>
+          <t>54040; 87447</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71751; 119766</t>
+          <t>91395; 126117</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72995; 110867</t>
+          <t>72524; 112079</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161703; 217308</t>
+          <t>162045; 217833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107506; 153648</t>
+          <t>106155; 153763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>141726; 207755</t>
+          <t>173994; 226066</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44131</t>
+          <t>49651</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4850; 19295</t>
+          <t>5444; 19984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7068; 23564</t>
+          <t>7163; 23520</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6837; 22832</t>
+          <t>5894; 22504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16604; 36649</t>
+          <t>18702; 38177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11192; 28321</t>
+          <t>11250; 28091</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8623; 26376</t>
+          <t>8854; 26195</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10877; 30234</t>
+          <t>11440; 30186</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13042; 27184</t>
+          <t>16476; 31725</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20102; 41297</t>
+          <t>19837; 40555</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19412; 43157</t>
+          <t>18450; 41984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22467; 48097</t>
+          <t>22532; 45139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33822; 58296</t>
+          <t>38858; 63348</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167378</t>
+          <t>183584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>248901</t>
+          <t>276814</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>416279</t>
+          <t>460398</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86111; 127563</t>
+          <t>84933; 127475</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>134848; 187010</t>
+          <t>134931; 186700</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98048; 140993</t>
+          <t>96875; 138532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129970; 196238</t>
+          <t>159344; 214469</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>140887; 192328</t>
+          <t>140324; 190043</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>292961; 363203</t>
+          <t>294250; 364973</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>169542; 223629</t>
+          <t>167187; 224215</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>206116; 279033</t>
+          <t>252508; 302474</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237495; 301003</t>
+          <t>235509; 302413</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>446865; 534063</t>
+          <t>440794; 530374</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>280127; 349906</t>
+          <t>278146; 351146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>355611; 462026</t>
+          <t>425069; 498291</t>
         </is>
       </c>
     </row>
